--- a/02_加值成品/八下/八下3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下3-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下3-3 中和與鹽　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下3-3 中和與鹽　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>酸與鹼反應生成？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>OH⁻</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>鹽和水</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>鹼中和酸</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>鹼性</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>中和</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>中和反應的離子式核心是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>移高中,國中重意義</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>H⁺+OH⁻→H₂O</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>H⁺與OH⁻結合成水釋出能量</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>指示劑變色終點</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>結合</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>中和是放熱還吸熱？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>氯化鈉</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>石灰(鹼性)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>離子化合物</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>放熱</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>升溫</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>pH小於7是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>鹼性中和酸</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>酸性</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>偏酸</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>pH等於7是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>胃酸</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>鹼性中和酸</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>純水</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>pH大於7是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>鹼性</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>鹽和水</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>離子化合物</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>偏鹼</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>食鹽是一種？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>鹽</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>酸性</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>氯化鈉和水</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>NaCl</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>胃藥的作用是中和？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>鹼性中和酸</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>胃酸</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>不一定</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>過多酸</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>酸鹼中和的產物是鹽和？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>鹽和水</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>石灰(鹼性)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>鹼性</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>中和</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>中和的核心是H⁺與什麼結合？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>離子化合物</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>OH⁻</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>氯化鈉和水</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>結合</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下3-3 中和與鹽　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下3-3 中和與鹽　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>鹽酸與氫氧化鈉中和生成？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>石灰(鹼性)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>氯化鈉和水</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>氯化鈉</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>NaCl+H₂O</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>中和反應溫度如何變？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>上升</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>氯化鈉</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>放熱</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>pH=3和pH=5誰較酸？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>H⁺+OH⁻→H₂O</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>酸性</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>氯化鈉</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>pH=3</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>數字小</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>酸性土壤可用什麼改良？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>胃酸</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>不一定</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>石灰(鹼性)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>中和</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>中和後溶液一定中性嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>離子化合物</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>不一定</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>視量與強弱</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>鹽多屬哪類化合物？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>離子化合物</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>鹼性</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>酸性</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>鹽和水</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>導電</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>牙膏偏鹼是為了？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>中和口腔酸</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>鹼性</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>OH⁻</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>護齒</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>pH=7的液體是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>氯化鈉和水</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>酸性</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>如純水</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>pH=1與pH=6誰酸性強？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>pH=3</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>pH=1</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>中和口腔酸</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>數字小</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>中和過程放熱使溫度？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>鹼性中和酸</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>上升</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>顏色改變時</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>放熱</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下3-3 中和與鹽　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下3-3 中和與鹽　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>胃酸過多吃鹼性胃藥原理？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>鹼中和過多H⁺減緩不適</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>H⁺+OH⁻→H₂O</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>H⁺與OH⁻結合成水釋出能量</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>移高中,國中重意義</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>中和</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>中和反應為何放熱？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>鹼中和過多H⁺減緩不適</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>移高中,國中重意義</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>H⁺與OH⁻結合成水釋出能量</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>指示劑變色終點</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>等量強酸強鹼中和後pH約？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>7(中性)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>pH=3</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>氯化鈉和水</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>恰中和</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>過量酸與少量鹼中和後呈？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>中和口腔酸</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>氯化鈉和水</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>酸性</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>酸剩餘</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>為何蜂螫(酸性)可塗小蘇打？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>鹼性中和酸</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>鹼性</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>緩解</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>如何用指示劑觀察中和終點？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>顏色改變時</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>氯化鈉和水</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>終點</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>鹽類命名由酸鹼決定,鹽酸+NaOH得？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>酸性</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>氯化鈉</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>命名</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何國中不算pH值？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>鹼中和過多H⁺減緩不適</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>指示劑變色終點</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>H⁺+OH⁻→H₂O</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>移高中,國中重意義</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>滴定中如何知道恰好中和？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>鹼中和過多H⁺減緩不適</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>H⁺與OH⁻結合成水釋出能量</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>指示劑變色終點</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>H⁺+OH⁻→H₂O</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>終點</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>酸性土壤加石灰改良的原理？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>鹼中和酸</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>中和口腔酸</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>鹽和水</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>中和</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下3-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>中和</t>
+          <t>中和：酸和鹼混合時會互相抵消對方的性質，反應後產生鹽和水這兩種新物質</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>結合</t>
+          <t>結合：酸提供的氫離子和鹼提供的氫氧根離子結合在一起，就形成了普通的水分子</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>升溫</t>
+          <t>升溫：氫離子和氫氧根結合成水的過程會釋放出能量，所以中和時溶液溫度會上升</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>偏酸</t>
+          <t>偏酸：pH值用來表示酸鹼程度，數字比7小就代表這杯溶液偏酸性</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>純水</t>
+          <t>純水：pH值剛好等於7表示這杯溶液既不偏酸也不偏鹼，像純水就是中性的例子</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>偏鹼</t>
+          <t>偏鹼：pH值用來表示酸鹼程度，數字比7大就代表這杯溶液偏鹼性</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>NaCl</t>
+          <t>NaCl：食鹽的化學名稱是氯化鈉，是鹽酸和氫氧化鈉中和之後會產生的一種鹽類</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>過多酸</t>
+          <t>過多酸：胃酸過多會讓人不舒服，胃藥中含有鹼性成分能把多餘的胃酸中和掉，緩解不適</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>中和</t>
+          <t>中和：酸和鹼發生中和反應時，會生成鹽和水這兩種產物</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>結合</t>
+          <t>結合：中和反應在微觀上的本質，就是酸解離出的H⁺和鹼解離出的OH⁻結合形成水分子</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>NaCl+H₂O</t>
+          <t>NaCl+H₂O：鹽酸提供的氫離子和氫氧化鈉提供的氫氧根結合成水，剩下的鈉和氯結合成氯化鈉</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>放熱：中和反應會釋放能量到溶液中，所以反應進行時可以觀察到溫度計的讀數逐漸上升</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>數字小</t>
+          <t>數字小：pH值越小代表溶液越偏酸性，所以pH等於3的溶液比pH等於5的溶液酸性更強</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>中和</t>
+          <t>中和：石灰是鹼性物質，撒進酸性土壤中可以中和土壤裡過多的酸，改善土壤品質</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>視量與強弱</t>
+          <t>視量與強弱：如果酸和鹼的量沒有恰好相等，反應後多出來的那一方會讓溶液仍然偏酸或偏鹼</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>導電</t>
+          <t>導電：鹽類大多是由帶正電和帶負電的離子組成，溶於水後能拆出離子，所以能導電</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>護齒</t>
+          <t>護齒：口腔中的細菌會產生酸性物質腐蝕牙齒，牙膏做成鹼性可以中和這些酸，保護牙齒</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>如純水</t>
+          <t>如純水：pH值剛好是7，代表這種液體既不偏酸也不偏鹼，純水就是典型的中性液體</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>數字小</t>
+          <t>數字小：pH值越小代表酸性越強，pH=1比pH=6的數字小，所以pH=1的酸性比較強</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>放熱：酸鹼中和是一種放熱反應，反應過程釋放出的熱能會使溶液溫度上升</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>中和</t>
+          <t>中和：鹼性胃藥中的成分會和胃裡多餘的氫離子結合，降低胃酸濃度，讓不舒服的感覺減緩</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：氫離子和氫氧根離子結合成穩定的水分子時，會把多餘的能量以熱的形式釋放出來</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>恰中和</t>
+          <t>恰中和：強酸和強鹼的量剛好相等時會完全反應完，沒有誰過量，所以溶液會呈現中性pH約為7</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>酸剩餘</t>
+          <t>酸剩餘：鹼的量不夠把所有的酸都反應完，所以反應後溶液裡還剩下多餘的酸，整體呈酸性</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>緩解</t>
+          <t>緩解：蜂螫注入的毒液偏酸性，小蘇打是鹼性物質，塗上去可以中和酸性毒液，減輕刺痛感</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>終點</t>
+          <t>終點：滴入指示劑後持續加入另一種試劑，當溶液顏色突然改變的那一刻，就代表酸鹼剛好中和完</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>命名</t>
+          <t>命名：鹽酸裡的氯和氫氧化鈉裡的鈉結合，依照命名規則就會產生氯化鈉這種鹽</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：pH值背後牽涉到較複雜的計算方式，這部分留到高中再學，國中先了解pH代表的意義就好</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>終點</t>
+          <t>終點：滴定實驗中會加入指示劑，當酸鹼恰好完全中和的那一刻，指示劑會出現顏色變化，這個時候稱為滴定終點，用來判斷是否恰好中和</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>中和</t>
+          <t>中和：石灰屬於鹼性物質，加入酸性土壤中可以和土壤裡的酸發生中和反應，降低土壤的酸性，改善土壤品質</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下3-3_三種難度測驗卷.xlsx
@@ -563,22 +563,22 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>中和口腔酸</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>鹽和水</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>氯化鈉和水</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>OH⁻</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>鹽和水</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>鹼中和酸</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>鹼性</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>鹽和水</t>
+          <t>酸性</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>鹽</t>
+          <t>放熱</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>離子化合物</t>
+          <t>水</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>酸性</t>
+          <t>鹼性</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>放熱</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>鹽和水</t>
+          <t>石灰(鹼性)</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>石灰(鹼性)</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>鹼性</t>
+          <t>離子化合物</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>石灰(鹼性)</t>
+          <t>鹼性中和酸</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>鹼性</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>氯化鈉</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>H⁺+OH⁻→H₂O</t>
+          <t>離子化合物</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>酸性</t>
+          <t>OH⁻</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>氯化鈉</t>
+          <t>pH=1</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1159,17 +1159,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>胃酸</t>
+          <t>鹼中和酸</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>不一定</t>
+          <t>氯化鈉和水</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>鹽</t>
+          <t>放熱</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1359,14 +1359,14 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>鹼中和酸</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
           <t>pH=3</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>鹽</t>
-        </is>
-      </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
           <t>pH=1</t>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>中和口腔酸</t>
+          <t>離子化合物</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>pH=3</t>
+          <t>離子化合物</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>顏色改變時</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鹼中和酸</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>氯化鈉和水</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>鹼性</t>
+          <t>酸性</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>上升</t>
+          <t>鹼性中和酸</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>酸性</t>
+          <t>放熱</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>鹽和水</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
